--- a/Design-Files/DC-UPS-v1.0/BOM/Client-BOM-DC-UPS-v1.0.xlsx
+++ b/Design-Files/DC-UPS-v1.0/BOM/Client-BOM-DC-UPS-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="705">
   <si>
     <t>#</t>
   </si>
@@ -2122,6 +2122,18 @@
   </si>
   <si>
     <t>DO NOT MOUNT</t>
+  </si>
+  <si>
+    <t>RT-C14-L00B-AA-09</t>
+  </si>
+  <si>
+    <t>Plugin AC Power Connectors ROHS</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legion </t>
   </si>
 </sst>
 </file>
@@ -2341,9 +2353,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2364,6 +2373,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2652,7 +2664,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K166"/>
+  <dimension ref="A1:K167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" style="4" bestFit="1" customWidth="1"/>
@@ -2676,9 +2688,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2748,7 +2760,7 @@
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B166" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B167" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -3961,8 +3973,8 @@
       </c>
       <c r="K41" s="7"/>
     </row>
-    <row r="42" spans="1:11" s="19" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="18"/>
+    <row r="42" spans="1:11" s="18" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="17"/>
       <c r="B42" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3970,28 +3982,28 @@
       <c r="C42" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="F42" s="15" t="s">
+      <c r="F42" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="G42" s="16" t="s">
+      <c r="G42" s="15" t="s">
         <v>446</v>
       </c>
-      <c r="H42" s="15" t="s">
+      <c r="H42" s="14" t="s">
         <v>557</v>
       </c>
-      <c r="I42" s="16" t="s">
+      <c r="I42" s="15" t="s">
         <v>633</v>
       </c>
-      <c r="J42" s="15">
-        <v>1</v>
-      </c>
-      <c r="K42" s="17" t="s">
+      <c r="J42" s="14">
+        <v>1</v>
+      </c>
+      <c r="K42" s="16" t="s">
         <v>700</v>
       </c>
     </row>
@@ -7328,28 +7340,28 @@
       <c r="C147" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D147" s="20" t="s">
+      <c r="D147" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="E147" s="21" t="s">
+      <c r="E147" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="F147" s="20" t="s">
+      <c r="F147" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="G147" s="21" t="s">
+      <c r="G147" s="20" t="s">
         <v>519</v>
       </c>
-      <c r="H147" s="20" t="s">
+      <c r="H147" s="19" t="s">
         <v>557</v>
       </c>
-      <c r="I147" s="21" t="s">
+      <c r="I147" s="20" t="s">
         <v>633</v>
       </c>
-      <c r="J147" s="20">
-        <v>1</v>
-      </c>
-      <c r="K147" s="17" t="s">
+      <c r="J147" s="19">
+        <v>1</v>
+      </c>
+      <c r="K147" s="16" t="s">
         <v>700</v>
       </c>
     </row>
@@ -7960,6 +7972,37 @@
         <v>1</v>
       </c>
       <c r="K166" s="9"/>
+    </row>
+    <row r="167" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B167" s="11">
+        <f t="shared" si="0"/>
+        <v>165</v>
+      </c>
+      <c r="C167" s="13" t="s">
+        <v>703</v>
+      </c>
+      <c r="D167" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="E167" s="10" t="s">
+        <v>702</v>
+      </c>
+      <c r="F167" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="G167" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="H167" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="I167" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="J167" s="9">
+        <v>1</v>
+      </c>
+      <c r="K167" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
